--- a/Day-1/1_excel.xlsx
+++ b/Day-1/1_excel.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="20115" windowHeight="7755" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$O$1:$R$17</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -52,6 +55,51 @@
   </si>
   <si>
     <t>Max Salary</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>no of senior</t>
+  </si>
+  <si>
+    <t>Above table is sorted by salary largest to smallest</t>
+  </si>
+  <si>
+    <t>added Filter</t>
+  </si>
+  <si>
+    <t>To find No of senior out of Category I used Count if</t>
   </si>
 </sst>
 </file>
@@ -83,7 +131,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -106,14 +154,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,11 +188,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,96 +534,96 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>22</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>20000</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>25</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>30000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>28</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>40000</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>24</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>25000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>30</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11">
         <f>SUM(C2:C6)</f>
         <v>165000</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11">
         <f>AVERAGE(C2:C6)</f>
         <v>33000</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11">
         <f>COUNT(C2:C6)</f>
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11">
         <f>MAX(C2:C6)</f>
         <v>50000</v>
       </c>
@@ -548,9 +636,722 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f>IF(B2&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2">
+        <v>34</v>
+      </c>
+      <c r="J2" s="2">
+        <v>65000</v>
+      </c>
+      <c r="K2" s="6" t="str">
+        <f>IF(I2&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>65000</v>
+      </c>
+      <c r="R2" s="6" t="str">
+        <f>IF(P2&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>30000</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <f t="shared" ref="D3:D16" si="0">IF(B3&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2">
+        <v>33</v>
+      </c>
+      <c r="J3" s="2">
+        <v>60000</v>
+      </c>
+      <c r="K3" s="6" t="str">
+        <f>IF(I3&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="2">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>60000</v>
+      </c>
+      <c r="R3" s="6" t="str">
+        <f>IF(P3&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
+        <v>40000</v>
+      </c>
+      <c r="D4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2">
+        <v>31</v>
+      </c>
+      <c r="J4" s="2">
+        <v>55000</v>
+      </c>
+      <c r="K4" s="6" t="str">
+        <f>IF(I4&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="2">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>55000</v>
+      </c>
+      <c r="R4" s="6" t="str">
+        <f>IF(P4&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="2">
+        <v>30</v>
+      </c>
+      <c r="J5" s="2">
+        <v>50000</v>
+      </c>
+      <c r="K5" s="6" t="str">
+        <f>IF(I5&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="2">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>50000</v>
+      </c>
+      <c r="R5" s="6" t="str">
+        <f>IF(P5&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
+        <v>50000</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2">
+        <v>45000</v>
+      </c>
+      <c r="K6" s="6" t="str">
+        <f>IF(I6&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="2">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>45000</v>
+      </c>
+      <c r="R6" s="6" t="str">
+        <f>IF(P6&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2">
+        <v>35000</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="2">
+        <v>28</v>
+      </c>
+      <c r="J7" s="2">
+        <v>42000</v>
+      </c>
+      <c r="K7" s="6" t="str">
+        <f>IF(I7&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="2">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>42000</v>
+      </c>
+      <c r="R7" s="6" t="str">
+        <f>IF(P7&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>22000</v>
+      </c>
+      <c r="D8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>28</v>
+      </c>
+      <c r="J8" s="2">
+        <v>40000</v>
+      </c>
+      <c r="K8" s="6" t="str">
+        <f>IF(I8&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="2">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>40000</v>
+      </c>
+      <c r="R8" s="6" t="str">
+        <f>IF(P8&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45000</v>
+      </c>
+      <c r="D9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="2">
+        <v>27</v>
+      </c>
+      <c r="J9" s="2">
+        <v>35000</v>
+      </c>
+      <c r="K9" s="6" t="str">
+        <f>IF(I9&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>35000</v>
+      </c>
+      <c r="R9" s="6" t="str">
+        <f>IF(P9&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2">
+        <v>32000</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2">
+        <v>26</v>
+      </c>
+      <c r="J10" s="2">
+        <v>32000</v>
+      </c>
+      <c r="K10" s="6" t="str">
+        <f>IF(I10&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="2">
+        <v>26</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>32000</v>
+      </c>
+      <c r="R10" s="6" t="str">
+        <f>IF(P10&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2">
+        <v>55000</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="2">
+        <v>26</v>
+      </c>
+      <c r="J11" s="2">
+        <v>31000</v>
+      </c>
+      <c r="K11" s="6" t="str">
+        <f>IF(I11&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P11" s="2">
+        <v>26</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>31000</v>
+      </c>
+      <c r="R11" s="6" t="str">
+        <f>IF(P11&gt;25,"Senior","Junior")</f>
+        <v>Senior</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2">
+        <v>18000</v>
+      </c>
+      <c r="D12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Junior</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>25</v>
+      </c>
+      <c r="J12" s="2">
+        <v>30000</v>
+      </c>
+      <c r="K12" s="6" t="str">
+        <f>IF(I12&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="2">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>30000</v>
+      </c>
+      <c r="R12" s="6" t="str">
+        <f>IF(P12&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="2">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2">
+        <v>60000</v>
+      </c>
+      <c r="D13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="2">
+        <v>24</v>
+      </c>
+      <c r="J13" s="2">
+        <v>25000</v>
+      </c>
+      <c r="K13" s="6" t="str">
+        <f>IF(I13&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="2">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>25000</v>
+      </c>
+      <c r="R13" s="6" t="str">
+        <f>IF(P13&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2">
+        <v>42000</v>
+      </c>
+      <c r="D14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2">
+        <v>23</v>
+      </c>
+      <c r="J14" s="2">
+        <v>22000</v>
+      </c>
+      <c r="K14" s="6" t="str">
+        <f>IF(I14&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P14" s="2">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>22000</v>
+      </c>
+      <c r="R14" s="6" t="str">
+        <f>IF(P14&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2">
+        <v>31000</v>
+      </c>
+      <c r="D15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="2">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2">
+        <v>20000</v>
+      </c>
+      <c r="K15" s="6" t="str">
+        <f>IF(I15&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="2">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>20000</v>
+      </c>
+      <c r="R15" s="6" t="str">
+        <f>IF(P15&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2">
+        <v>65000</v>
+      </c>
+      <c r="D16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Senior</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="2">
+        <v>21</v>
+      </c>
+      <c r="J16" s="2">
+        <v>18000</v>
+      </c>
+      <c r="K16" s="6" t="str">
+        <f>IF(I16&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>18000</v>
+      </c>
+      <c r="R16" s="6" t="str">
+        <f>IF(P16&gt;25,"Senior","Junior")</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="11">
+        <f>COUNTIF(D2:D16,"Senior")</f>
+        <v>10</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="11">
+        <f>COUNTIF(K2:K16,"Senior")</f>
+        <v>10</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="11">
+        <f>COUNTIF(R2:R16,"Senior")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B18" s="14"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B19" s="13"/>
+      <c r="G19" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="O19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19" s="12"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="R20" s="12"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="O1:R17"/>
+  <sortState ref="H2:K17">
+    <sortCondition descending="1" ref="J2:J17"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
